--- a/artfynd/A 958-2025 artfynd.xlsx
+++ b/artfynd/A 958-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122289139</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 958-2025 artfynd.xlsx
+++ b/artfynd/A 958-2025 artfynd.xlsx
@@ -817,11 +817,6 @@
       <c r="E3" t="n">
         <v>100049</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 958-2025 artfynd.xlsx
+++ b/artfynd/A 958-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122289139</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,6 +816,11 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 958-2025 artfynd.xlsx
+++ b/artfynd/A 958-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122289139</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 958-2025 artfynd.xlsx
+++ b/artfynd/A 958-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>97102310</v>
       </c>
       <c r="B2" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567148.0309774873</v>
+        <v>567148</v>
       </c>
       <c r="R2" t="n">
-        <v>6416916.587888868</v>
+        <v>6416917</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,16 +787,11 @@
         <v>122289139</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -911,6 +891,111 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123591880</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 958, Frö, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567234</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6416995</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
